--- a/business_forms/049_retail_cloud_solution_certification_application_form--business_forms.xlsx
+++ b/business_forms/049_retail_cloud_solution_certification_application_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>submission_date_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Submission Date</t>
+          <t>Submission Date 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>submission_time_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Submission Time</t>
+          <t>Submission Time 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>submission_date_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Submission Date</t>
+          <t>Submission Date 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>submission_time_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Submission Time</t>
+          <t>Submission Time 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'vendor',_'value':_'vendor'}</t>
+          <t>vendor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Vendor', 'value': 'Vendor'}</t>
+          <t>Vendor</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'technology_team',_'value':_'technology_team'}</t>
+          <t>technology_team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Technology team', 'value': 'Technology team'}</t>
+          <t>Technology team</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cloud',_'value':_'cloud'}</t>
+          <t>cloud</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Cloud', 'value': 'Cloud'}</t>
+          <t>Cloud</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'non-cloud',_'value':_'non-cloud'}</t>
+          <t>non-cloud</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Non-Cloud', 'value': 'Non-Cloud'}</t>
+          <t>Non-Cloud</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'hybrid',_'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Hybrid', 'value': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Approved', 'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rejected',_'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rejected', 'value': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'retail',_'value':_'retail'}</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Retail', 'value': 'Retail'}</t>
+          <t>Retail</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'non-retail',_'value':_'non-retail'}</t>
+          <t>non-retail</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Non-Retail', 'value': 'Non-Retail'}</t>
+          <t>Non-Retail</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full',_'value':_'full'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Full', 'value': 'Full'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'incremental',_'value':_'incremental'}</t>
+          <t>incremental</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Incremental', 'value': 'Incremental'}</t>
+          <t>Incremental</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
